--- a/Excel Project/Retail_Sales_Dashboard.xlsx
+++ b/Excel Project/Retail_Sales_Dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6129d808c8960a80/Documents/DA Project/Excel Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{9867A814-C540-4014-8DC5-4208C6DF2043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6B46241E-5D06-4004-8A59-18993B5836F1}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="13_ncr:1_{9867A814-C540-4014-8DC5-4208C6DF2043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FD540C6-6DC4-4337-85D2-B42EAD48C7DF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4323,7 +4323,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
-    <numFmt numFmtId="166" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -4453,7 +4453,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4466,12 +4466,29 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4481,27 +4498,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7760,6 +7756,630 @@
               <a:gs pos="100000">
                 <a:schemeClr val="accent1">
                   <a:tint val="54000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="84"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:shade val="40000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="40000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="40000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="85"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:shade val="51000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="51000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="51000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="86"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:shade val="62000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="62000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="62000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="87"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:shade val="73000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="73000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="73000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="88"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:shade val="83000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="83000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="83000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="89"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:shade val="94000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="94000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:shade val="94000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="90"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:tint val="95000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="95000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="95000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="91"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:tint val="84000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="84000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="84000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="92"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:tint val="74000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="74000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="74000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="93"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:tint val="63000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="63000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="63000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="94"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:tint val="52000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="52000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="52000"/>
+                  <a:shade val="94000"/>
+                  <a:satMod val="135000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="16200000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="95"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:tint val="41000"/>
+                  <a:shade val="51000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="80000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="41000"/>
+                  <a:shade val="93000"/>
+                  <a:satMod val="130000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:tint val="41000"/>
                   <a:shade val="94000"/>
                   <a:satMod val="135000"/>
                 </a:schemeClr>
@@ -15541,12 +16161,12 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>3695700</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>68580</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1417320</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
@@ -37313,6 +37933,1044 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7996EE8E-41CE-40DB-92E1-3A9F82F22B95}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+  <location ref="H3:I15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="19">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="537">
+        <item x="532"/>
+        <item x="253"/>
+        <item x="358"/>
+        <item x="58"/>
+        <item x="364"/>
+        <item x="415"/>
+        <item x="119"/>
+        <item x="141"/>
+        <item x="136"/>
+        <item x="283"/>
+        <item x="370"/>
+        <item x="91"/>
+        <item x="393"/>
+        <item x="290"/>
+        <item x="443"/>
+        <item x="213"/>
+        <item x="123"/>
+        <item x="40"/>
+        <item x="22"/>
+        <item x="106"/>
+        <item x="178"/>
+        <item x="319"/>
+        <item x="438"/>
+        <item x="44"/>
+        <item x="354"/>
+        <item x="7"/>
+        <item x="368"/>
+        <item x="375"/>
+        <item x="256"/>
+        <item x="460"/>
+        <item x="171"/>
+        <item x="336"/>
+        <item x="219"/>
+        <item x="28"/>
+        <item x="429"/>
+        <item x="479"/>
+        <item x="188"/>
+        <item x="530"/>
+        <item x="6"/>
+        <item x="466"/>
+        <item x="32"/>
+        <item x="166"/>
+        <item x="489"/>
+        <item x="53"/>
+        <item x="59"/>
+        <item x="342"/>
+        <item x="323"/>
+        <item x="168"/>
+        <item x="492"/>
+        <item x="69"/>
+        <item x="395"/>
+        <item x="361"/>
+        <item x="369"/>
+        <item x="279"/>
+        <item x="52"/>
+        <item x="79"/>
+        <item x="93"/>
+        <item x="414"/>
+        <item x="237"/>
+        <item x="92"/>
+        <item x="345"/>
+        <item x="397"/>
+        <item x="27"/>
+        <item x="193"/>
+        <item x="515"/>
+        <item x="304"/>
+        <item x="157"/>
+        <item x="314"/>
+        <item x="504"/>
+        <item x="217"/>
+        <item x="135"/>
+        <item x="305"/>
+        <item x="412"/>
+        <item x="4"/>
+        <item x="164"/>
+        <item x="181"/>
+        <item x="57"/>
+        <item x="388"/>
+        <item x="416"/>
+        <item x="30"/>
+        <item x="350"/>
+        <item x="513"/>
+        <item x="223"/>
+        <item x="315"/>
+        <item x="160"/>
+        <item x="334"/>
+        <item x="75"/>
+        <item x="498"/>
+        <item x="131"/>
+        <item x="88"/>
+        <item x="308"/>
+        <item x="191"/>
+        <item x="491"/>
+        <item x="407"/>
+        <item x="321"/>
+        <item x="64"/>
+        <item x="56"/>
+        <item x="261"/>
+        <item x="284"/>
+        <item x="215"/>
+        <item x="98"/>
+        <item x="386"/>
+        <item x="275"/>
+        <item x="363"/>
+        <item x="482"/>
+        <item x="84"/>
+        <item x="496"/>
+        <item x="436"/>
+        <item x="483"/>
+        <item x="19"/>
+        <item x="426"/>
+        <item x="343"/>
+        <item x="154"/>
+        <item x="225"/>
+        <item x="514"/>
+        <item x="72"/>
+        <item x="516"/>
+        <item x="209"/>
+        <item x="437"/>
+        <item x="374"/>
+        <item x="145"/>
+        <item x="42"/>
+        <item x="311"/>
+        <item x="260"/>
+        <item x="158"/>
+        <item x="190"/>
+        <item x="216"/>
+        <item x="384"/>
+        <item x="424"/>
+        <item x="48"/>
+        <item x="78"/>
+        <item x="149"/>
+        <item x="172"/>
+        <item x="326"/>
+        <item x="404"/>
+        <item x="99"/>
+        <item x="353"/>
+        <item x="232"/>
+        <item x="194"/>
+        <item x="325"/>
+        <item x="229"/>
+        <item x="81"/>
+        <item x="200"/>
+        <item x="367"/>
+        <item x="328"/>
+        <item x="189"/>
+        <item x="430"/>
+        <item x="46"/>
+        <item x="127"/>
+        <item x="401"/>
+        <item x="339"/>
+        <item x="421"/>
+        <item x="184"/>
+        <item x="287"/>
+        <item x="206"/>
+        <item x="0"/>
+        <item x="310"/>
+        <item x="23"/>
+        <item x="423"/>
+        <item x="107"/>
+        <item x="14"/>
+        <item x="103"/>
+        <item x="89"/>
+        <item x="173"/>
+        <item x="385"/>
+        <item x="522"/>
+        <item x="470"/>
+        <item x="399"/>
+        <item x="39"/>
+        <item x="488"/>
+        <item x="262"/>
+        <item x="248"/>
+        <item x="152"/>
+        <item x="109"/>
+        <item x="497"/>
+        <item x="512"/>
+        <item x="518"/>
+        <item x="182"/>
+        <item x="378"/>
+        <item x="371"/>
+        <item x="24"/>
+        <item x="330"/>
+        <item x="459"/>
+        <item x="47"/>
+        <item x="273"/>
+        <item x="204"/>
+        <item x="139"/>
+        <item x="485"/>
+        <item x="365"/>
+        <item x="265"/>
+        <item x="13"/>
+        <item x="286"/>
+        <item x="113"/>
+        <item x="31"/>
+        <item x="62"/>
+        <item x="320"/>
+        <item x="270"/>
+        <item x="87"/>
+        <item x="38"/>
+        <item x="86"/>
+        <item x="259"/>
+        <item x="242"/>
+        <item x="510"/>
+        <item x="338"/>
+        <item x="147"/>
+        <item x="300"/>
+        <item x="524"/>
+        <item x="201"/>
+        <item x="332"/>
+        <item x="73"/>
+        <item x="128"/>
+        <item x="15"/>
+        <item x="250"/>
+        <item x="351"/>
+        <item x="104"/>
+        <item x="169"/>
+        <item x="221"/>
+        <item x="435"/>
+        <item x="505"/>
+        <item x="117"/>
+        <item x="96"/>
+        <item x="77"/>
+        <item x="291"/>
+        <item x="243"/>
+        <item x="255"/>
+        <item x="387"/>
+        <item x="452"/>
+        <item x="347"/>
+        <item x="400"/>
+        <item x="228"/>
+        <item x="500"/>
+        <item x="468"/>
+        <item x="316"/>
+        <item x="282"/>
+        <item x="508"/>
+        <item x="11"/>
+        <item x="493"/>
+        <item x="196"/>
+        <item x="187"/>
+        <item x="55"/>
+        <item x="34"/>
+        <item x="212"/>
+        <item x="20"/>
+        <item x="457"/>
+        <item x="3"/>
+        <item x="301"/>
+        <item x="234"/>
+        <item x="322"/>
+        <item x="195"/>
+        <item x="376"/>
+        <item x="45"/>
+        <item x="413"/>
+        <item x="288"/>
+        <item x="389"/>
+        <item x="105"/>
+        <item x="278"/>
+        <item x="382"/>
+        <item x="372"/>
+        <item x="210"/>
+        <item x="153"/>
+        <item x="276"/>
+        <item x="126"/>
+        <item x="61"/>
+        <item x="95"/>
+        <item x="90"/>
+        <item x="494"/>
+        <item x="309"/>
+        <item x="317"/>
+        <item x="138"/>
+        <item x="50"/>
+        <item x="274"/>
+        <item x="63"/>
+        <item x="464"/>
+        <item x="82"/>
+        <item x="133"/>
+        <item x="159"/>
+        <item x="520"/>
+        <item x="140"/>
+        <item x="523"/>
+        <item x="467"/>
+        <item x="299"/>
+        <item x="120"/>
+        <item x="481"/>
+        <item x="349"/>
+        <item x="455"/>
+        <item x="74"/>
+        <item x="186"/>
+        <item x="454"/>
+        <item x="406"/>
+        <item x="54"/>
+        <item x="94"/>
+        <item x="230"/>
+        <item x="227"/>
+        <item x="76"/>
+        <item x="137"/>
+        <item x="26"/>
+        <item x="355"/>
+        <item x="461"/>
+        <item x="418"/>
+        <item x="257"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="447"/>
+        <item x="511"/>
+        <item x="448"/>
+        <item x="420"/>
+        <item x="293"/>
+        <item x="185"/>
+        <item x="130"/>
+        <item x="263"/>
+        <item x="297"/>
+        <item x="396"/>
+        <item x="289"/>
+        <item x="203"/>
+        <item x="80"/>
+        <item x="156"/>
+        <item x="199"/>
+        <item x="327"/>
+        <item x="373"/>
+        <item x="264"/>
+        <item x="246"/>
+        <item x="251"/>
+        <item x="296"/>
+        <item x="125"/>
+        <item x="528"/>
+        <item x="294"/>
+        <item x="390"/>
+        <item x="134"/>
+        <item x="222"/>
+        <item x="37"/>
+        <item x="1"/>
+        <item x="9"/>
+        <item x="519"/>
+        <item x="473"/>
+        <item x="151"/>
+        <item x="108"/>
+        <item x="318"/>
+        <item x="517"/>
+        <item x="529"/>
+        <item x="85"/>
+        <item x="335"/>
+        <item x="463"/>
+        <item x="238"/>
+        <item x="509"/>
+        <item x="97"/>
+        <item x="476"/>
+        <item x="202"/>
+        <item x="409"/>
+        <item x="475"/>
+        <item x="356"/>
+        <item x="240"/>
+        <item x="391"/>
+        <item x="2"/>
+        <item x="474"/>
+        <item x="129"/>
+        <item x="83"/>
+        <item x="380"/>
+        <item x="249"/>
+        <item x="176"/>
+        <item x="306"/>
+        <item x="398"/>
+        <item x="155"/>
+        <item x="402"/>
+        <item x="205"/>
+        <item x="165"/>
+        <item x="115"/>
+        <item x="329"/>
+        <item x="428"/>
+        <item x="65"/>
+        <item x="179"/>
+        <item x="359"/>
+        <item x="51"/>
+        <item x="408"/>
+        <item x="360"/>
+        <item x="244"/>
+        <item x="295"/>
+        <item x="277"/>
+        <item x="241"/>
+        <item x="124"/>
+        <item x="324"/>
+        <item x="33"/>
+        <item x="465"/>
+        <item x="392"/>
+        <item x="377"/>
+        <item x="444"/>
+        <item x="456"/>
+        <item x="352"/>
+        <item x="337"/>
+        <item x="183"/>
+        <item x="348"/>
+        <item x="235"/>
+        <item x="132"/>
+        <item x="411"/>
+        <item x="218"/>
+        <item x="434"/>
+        <item x="458"/>
+        <item x="495"/>
+        <item x="49"/>
+        <item x="122"/>
+        <item x="68"/>
+        <item x="198"/>
+        <item x="366"/>
+        <item x="231"/>
+        <item x="462"/>
+        <item x="535"/>
+        <item x="502"/>
+        <item x="307"/>
+        <item x="258"/>
+        <item x="247"/>
+        <item x="146"/>
+        <item x="272"/>
+        <item x="526"/>
+        <item x="121"/>
+        <item x="357"/>
+        <item x="531"/>
+        <item x="111"/>
+        <item x="100"/>
+        <item x="18"/>
+        <item x="271"/>
+        <item x="480"/>
+        <item x="70"/>
+        <item x="379"/>
+        <item x="346"/>
+        <item x="469"/>
+        <item x="233"/>
+        <item x="439"/>
+        <item x="292"/>
+        <item x="192"/>
+        <item x="268"/>
+        <item x="503"/>
+        <item x="403"/>
+        <item x="381"/>
+        <item x="333"/>
+        <item x="150"/>
+        <item x="245"/>
+        <item x="440"/>
+        <item x="175"/>
+        <item x="432"/>
+        <item x="303"/>
+        <item x="197"/>
+        <item x="431"/>
+        <item x="163"/>
+        <item x="422"/>
+        <item x="102"/>
+        <item x="8"/>
+        <item x="220"/>
+        <item x="383"/>
+        <item x="341"/>
+        <item x="302"/>
+        <item x="224"/>
+        <item x="254"/>
+        <item x="445"/>
+        <item x="533"/>
+        <item x="148"/>
+        <item x="433"/>
+        <item x="170"/>
+        <item x="161"/>
+        <item x="211"/>
+        <item x="527"/>
+        <item x="41"/>
+        <item x="313"/>
+        <item x="362"/>
+        <item x="177"/>
+        <item x="25"/>
+        <item x="21"/>
+        <item x="17"/>
+        <item x="487"/>
+        <item x="344"/>
+        <item x="312"/>
+        <item x="71"/>
+        <item x="12"/>
+        <item x="442"/>
+        <item x="394"/>
+        <item x="226"/>
+        <item x="471"/>
+        <item x="143"/>
+        <item x="29"/>
+        <item x="43"/>
+        <item x="144"/>
+        <item x="112"/>
+        <item x="16"/>
+        <item x="236"/>
+        <item x="252"/>
+        <item x="162"/>
+        <item x="453"/>
+        <item x="419"/>
+        <item x="118"/>
+        <item x="506"/>
+        <item x="484"/>
+        <item x="486"/>
+        <item x="478"/>
+        <item x="174"/>
+        <item x="67"/>
+        <item x="410"/>
+        <item x="449"/>
+        <item x="142"/>
+        <item x="269"/>
+        <item x="267"/>
+        <item x="450"/>
+        <item x="425"/>
+        <item x="207"/>
+        <item x="534"/>
+        <item x="110"/>
+        <item x="180"/>
+        <item x="417"/>
+        <item x="101"/>
+        <item x="298"/>
+        <item x="114"/>
+        <item x="441"/>
+        <item x="477"/>
+        <item x="499"/>
+        <item x="167"/>
+        <item x="10"/>
+        <item x="405"/>
+        <item x="281"/>
+        <item x="331"/>
+        <item x="490"/>
+        <item x="427"/>
+        <item x="501"/>
+        <item x="340"/>
+        <item x="446"/>
+        <item x="285"/>
+        <item x="208"/>
+        <item x="214"/>
+        <item x="451"/>
+        <item x="280"/>
+        <item x="472"/>
+        <item x="525"/>
+        <item x="507"/>
+        <item x="66"/>
+        <item x="521"/>
+        <item x="60"/>
+        <item x="5"/>
+        <item x="239"/>
+        <item x="116"/>
+        <item x="266"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="17">
+        <item x="7"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="12"/>
+        <item x="15"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="14"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="13">
+        <item x="11"/>
+        <item x="5"/>
+        <item x="3"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="7"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="4" showAll="0">
+      <items count="331">
+        <item x="264"/>
+        <item x="31"/>
+        <item x="192"/>
+        <item x="280"/>
+        <item x="131"/>
+        <item x="91"/>
+        <item x="184"/>
+        <item x="19"/>
+        <item x="203"/>
+        <item x="289"/>
+        <item x="199"/>
+        <item x="166"/>
+        <item x="265"/>
+        <item x="95"/>
+        <item x="70"/>
+        <item x="266"/>
+        <item x="172"/>
+        <item x="40"/>
+        <item x="18"/>
+        <item x="57"/>
+        <item x="159"/>
+        <item x="251"/>
+        <item x="55"/>
+        <item x="119"/>
+        <item x="193"/>
+        <item x="82"/>
+        <item x="133"/>
+        <item x="155"/>
+        <item x="128"/>
+        <item x="107"/>
+        <item x="294"/>
+        <item x="205"/>
+        <item x="129"/>
+        <item x="51"/>
+        <item x="115"/>
+        <item x="94"/>
+        <item x="104"/>
+        <item x="67"/>
+        <item x="271"/>
+        <item x="6"/>
+        <item x="202"/>
+        <item x="34"/>
+        <item x="149"/>
+        <item x="44"/>
+        <item x="135"/>
+        <item x="153"/>
+        <item x="183"/>
+        <item x="14"/>
+        <item x="71"/>
+        <item x="144"/>
+        <item x="32"/>
+        <item x="260"/>
+        <item x="298"/>
+        <item x="238"/>
+        <item x="33"/>
+        <item x="142"/>
+        <item x="219"/>
+        <item x="243"/>
+        <item x="77"/>
+        <item x="296"/>
+        <item x="151"/>
+        <item x="256"/>
+        <item x="209"/>
+        <item x="242"/>
+        <item x="187"/>
+        <item x="117"/>
+        <item x="249"/>
+        <item x="164"/>
+        <item x="175"/>
+        <item x="27"/>
+        <item x="68"/>
+        <item x="61"/>
+        <item x="41"/>
+        <item x="140"/>
+        <item x="21"/>
+        <item x="120"/>
+        <item x="165"/>
+        <item x="146"/>
+        <item x="278"/>
+        <item x="308"/>
+        <item x="97"/>
+        <item x="4"/>
+        <item x="241"/>
+        <item x="309"/>
+        <item x="111"/>
+        <item x="99"/>
+        <item x="114"/>
+        <item x="37"/>
+        <item x="329"/>
+        <item x="319"/>
+        <item x="110"/>
+        <item x="83"/>
+        <item x="254"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="324"/>
+        <item x="143"/>
+        <item x="288"/>
+        <item x="220"/>
+        <item x="88"/>
+        <item x="148"/>
+        <item x="274"/>
+        <item x="103"/>
+        <item x="124"/>
+        <item x="39"/>
+        <item x="214"/>
+        <item x="277"/>
+        <item x="5"/>
+        <item x="305"/>
+        <item x="318"/>
+        <item x="72"/>
+        <item x="287"/>
+        <item x="116"/>
+        <item x="112"/>
+        <item x="236"/>
+        <item x="321"/>
+        <item x="237"/>
+        <item x="178"/>
+        <item x="162"/>
+        <item x="36"/>
+        <item x="89"/>
+        <item x="224"/>
+        <item x="198"/>
+        <item x="284"/>
+        <item x="190"/>
+        <item x="62"/>
+        <item x="169"/>
+        <item x="204"/>
+        <item x="98"/>
+        <item x="22"/>
+        <item x="253"/>
+        <item x="50"/>
+        <item x="170"/>
+        <item x="156"/>
+        <item x="317"/>
+        <item x="15"/>
+        <item x="81"/>
+        <item x="85"/>
+        <item x="157"/>
+        <item x="59"/>
+        <item x="66"/>
+        <item x="234"/>
+        <item x="245"/>
+        <item x="141"/>
+        <item x="229"/>
+        <item x="54"/>
+        <item x="263"/>
+        <item x="125"/>
+        <item x="315"/>
+        <item x="3"/>
+        <item x="160"/>
+        <item x="240"/>
+        <item x="200"/>
+        <item x="171"/>
+        <item x="13"/>
+        <item x="176"/>
+        <item x="230"/>
+        <item x="106"/>
+        <item x="20"/>
+        <item x="75"/>
+        <item x="16"/>
+        <item x="228"/>
+        <item x="53"/>
+        <item x="215"/>
+        <item x="258"/>
+        <item x="320"/>
+        <item x="268"/>
+        <item x="255"/>
+        <item x="262"/>
+        <item x="206"/>
+        <item x="173"/>
+        <item x="225"/>
+        <item x="180"/>
+        <item x="325"/>
+        <item x="191"/>
+        <item x="300"/>
+        <item x="127"/>
+        <item x="207"/>
+        <item x="47"/>
+        <item x="259"/>
+        <item x="306"/>
+        <item x="292"/>
+        <item x="10"/>
+        <item x="314"/>
+        <item x="76"/>
+        <item x="322"/>
+        <item x="113"/>
+        <item x="42"/>
+        <item x="17"/>
+        <item x="186"/>
+        <item x="73"/>
+        <item x="26"/>
+        <item x="0"/>
+        <item x="293"/>
+        <item x="87"/>
+        <item x="56"/>
+        <item x="212"/>
+        <item x="312"/>
+        <item x="247"/>
+        <item x="132"/>
+        <item x="161"/>
+        <item x="101"/>
+        <item x="28"/>
+        <item x="147"/>
+        <item x="233"/>
+        <item x="210"/>
+        <item x="137"/>
+        <item x="45"/>
+        <item x="195"/>
+        <item x="181"/>
+        <item x="313"/>
+        <item x="261"/>
+        <item x="239"/>
+        <item x="307"/>
+        <item x="299"/>
+        <item x="250"/>
+        <item x="58"/>
+        <item x="235"/>
+        <item x="188"/>
+        <item x="316"/>
+        <item x="189"/>
+        <item x="23"/>
+        <item x="138"/>
+        <item x="226"/>
+        <item x="244"/>
+        <item x="213"/>
+        <item x="96"/>
+        <item x="38"/>
+        <item x="168"/>
+        <item x="86"/>
+        <item x="167"/>
+        <item x="48"/>
+        <item x="273"/>
+        <item x="11"/>
+        <item x="201"/>
+        <item x="78"/>
+        <item x="276"/>
+        <item x="63"/>
+        <item x="100"/>
+        <item x="60"/>
+        <item x="49"/>
+        <item x="327"/>
+        <item x="182"/>
+        <item x="69"/>
+        <item x="64"/>
+        <item x="248"/>
+        <item x="270"/>
+        <item x="102"/>
+        <item x="24"/>
+        <item x="8"/>
+        <item x="139"/>
+        <item x="279"/>
+        <item x="12"/>
+        <item x="328"/>
+        <item x="179"/>
+        <item x="295"/>
+        <item x="158"/>
+        <item x="109"/>
+        <item x="275"/>
+        <item x="123"/>
+        <item x="282"/>
+        <item x="25"/>
+        <item x="145"/>
+        <item x="194"/>
+        <item x="218"/>
+        <item x="46"/>
+        <item x="303"/>
+        <item x="154"/>
+        <item x="35"/>
+        <item x="208"/>
+        <item x="122"/>
+        <item x="105"/>
+        <item x="126"/>
+        <item x="80"/>
+        <item x="108"/>
+        <item x="231"/>
+        <item x="281"/>
+        <item x="272"/>
+        <item x="150"/>
+        <item x="7"/>
+        <item x="304"/>
+        <item x="177"/>
+        <item x="163"/>
+        <item x="257"/>
+        <item x="65"/>
+        <item x="121"/>
+        <item x="79"/>
+        <item x="227"/>
+        <item x="134"/>
+        <item x="283"/>
+        <item x="232"/>
+        <item x="90"/>
+        <item x="152"/>
+        <item x="301"/>
+        <item x="311"/>
+        <item x="130"/>
+        <item x="197"/>
+        <item x="267"/>
+        <item x="30"/>
+        <item x="217"/>
+        <item x="297"/>
+        <item x="302"/>
+        <item x="84"/>
+        <item x="216"/>
+        <item x="74"/>
+        <item x="1"/>
+        <item x="222"/>
+        <item x="196"/>
+        <item x="118"/>
+        <item x="136"/>
+        <item x="221"/>
+        <item x="252"/>
+        <item x="52"/>
+        <item x="211"/>
+        <item x="290"/>
+        <item x="223"/>
+        <item x="174"/>
+        <item x="291"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="185"/>
+        <item x="310"/>
+        <item x="269"/>
+        <item x="323"/>
+        <item x="286"/>
+        <item x="246"/>
+        <item x="43"/>
+        <item x="326"/>
+        <item x="285"/>
+        <item x="29"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="4" showAll="0"/>
+    <pivotField dataField="1" numFmtId="4" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="14">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0" defaultSubtotal="0"/>
+    <pivotField showAll="0" defaultSubtotal="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="12">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Profit" fld="12" baseField="0" baseItem="0" numFmtId="4"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="7" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4955E7C9-05EA-4910-80D7-ED0CAB68F354}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="E3:F16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -38660,7 +40318,7 @@
   <dataFields count="1">
     <dataField name="Sum of Discount" fld="11" baseField="0" baseItem="0" numFmtId="4"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="14">
     <chartFormat chart="0" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -38679,6 +40337,150 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="5" format="84">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="85">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="86">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="87">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="88">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="89">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="90">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="91">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="92">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="93">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="94">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="10"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="95">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="11"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
@@ -38692,7 +40494,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{964C9B0A-3B45-4092-8307-F809A04D6023}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:C16" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -39772,7 +41574,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{71527C9C-3489-4498-8E27-9FDC1E4608EA}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="B20:C24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="19">
@@ -40793,7 +42595,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{09CD836A-B84A-4C84-B5F6-7EE337448648}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="K3:Q10" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="19">
@@ -42995,1044 +44797,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7996EE8E-41CE-40DB-92E1-3A9F82F22B95}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
-  <location ref="H3:I15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="19">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="537">
-        <item x="532"/>
-        <item x="253"/>
-        <item x="358"/>
-        <item x="58"/>
-        <item x="364"/>
-        <item x="415"/>
-        <item x="119"/>
-        <item x="141"/>
-        <item x="136"/>
-        <item x="283"/>
-        <item x="370"/>
-        <item x="91"/>
-        <item x="393"/>
-        <item x="290"/>
-        <item x="443"/>
-        <item x="213"/>
-        <item x="123"/>
-        <item x="40"/>
-        <item x="22"/>
-        <item x="106"/>
-        <item x="178"/>
-        <item x="319"/>
-        <item x="438"/>
-        <item x="44"/>
-        <item x="354"/>
-        <item x="7"/>
-        <item x="368"/>
-        <item x="375"/>
-        <item x="256"/>
-        <item x="460"/>
-        <item x="171"/>
-        <item x="336"/>
-        <item x="219"/>
-        <item x="28"/>
-        <item x="429"/>
-        <item x="479"/>
-        <item x="188"/>
-        <item x="530"/>
-        <item x="6"/>
-        <item x="466"/>
-        <item x="32"/>
-        <item x="166"/>
-        <item x="489"/>
-        <item x="53"/>
-        <item x="59"/>
-        <item x="342"/>
-        <item x="323"/>
-        <item x="168"/>
-        <item x="492"/>
-        <item x="69"/>
-        <item x="395"/>
-        <item x="361"/>
-        <item x="369"/>
-        <item x="279"/>
-        <item x="52"/>
-        <item x="79"/>
-        <item x="93"/>
-        <item x="414"/>
-        <item x="237"/>
-        <item x="92"/>
-        <item x="345"/>
-        <item x="397"/>
-        <item x="27"/>
-        <item x="193"/>
-        <item x="515"/>
-        <item x="304"/>
-        <item x="157"/>
-        <item x="314"/>
-        <item x="504"/>
-        <item x="217"/>
-        <item x="135"/>
-        <item x="305"/>
-        <item x="412"/>
-        <item x="4"/>
-        <item x="164"/>
-        <item x="181"/>
-        <item x="57"/>
-        <item x="388"/>
-        <item x="416"/>
-        <item x="30"/>
-        <item x="350"/>
-        <item x="513"/>
-        <item x="223"/>
-        <item x="315"/>
-        <item x="160"/>
-        <item x="334"/>
-        <item x="75"/>
-        <item x="498"/>
-        <item x="131"/>
-        <item x="88"/>
-        <item x="308"/>
-        <item x="191"/>
-        <item x="491"/>
-        <item x="407"/>
-        <item x="321"/>
-        <item x="64"/>
-        <item x="56"/>
-        <item x="261"/>
-        <item x="284"/>
-        <item x="215"/>
-        <item x="98"/>
-        <item x="386"/>
-        <item x="275"/>
-        <item x="363"/>
-        <item x="482"/>
-        <item x="84"/>
-        <item x="496"/>
-        <item x="436"/>
-        <item x="483"/>
-        <item x="19"/>
-        <item x="426"/>
-        <item x="343"/>
-        <item x="154"/>
-        <item x="225"/>
-        <item x="514"/>
-        <item x="72"/>
-        <item x="516"/>
-        <item x="209"/>
-        <item x="437"/>
-        <item x="374"/>
-        <item x="145"/>
-        <item x="42"/>
-        <item x="311"/>
-        <item x="260"/>
-        <item x="158"/>
-        <item x="190"/>
-        <item x="216"/>
-        <item x="384"/>
-        <item x="424"/>
-        <item x="48"/>
-        <item x="78"/>
-        <item x="149"/>
-        <item x="172"/>
-        <item x="326"/>
-        <item x="404"/>
-        <item x="99"/>
-        <item x="353"/>
-        <item x="232"/>
-        <item x="194"/>
-        <item x="325"/>
-        <item x="229"/>
-        <item x="81"/>
-        <item x="200"/>
-        <item x="367"/>
-        <item x="328"/>
-        <item x="189"/>
-        <item x="430"/>
-        <item x="46"/>
-        <item x="127"/>
-        <item x="401"/>
-        <item x="339"/>
-        <item x="421"/>
-        <item x="184"/>
-        <item x="287"/>
-        <item x="206"/>
-        <item x="0"/>
-        <item x="310"/>
-        <item x="23"/>
-        <item x="423"/>
-        <item x="107"/>
-        <item x="14"/>
-        <item x="103"/>
-        <item x="89"/>
-        <item x="173"/>
-        <item x="385"/>
-        <item x="522"/>
-        <item x="470"/>
-        <item x="399"/>
-        <item x="39"/>
-        <item x="488"/>
-        <item x="262"/>
-        <item x="248"/>
-        <item x="152"/>
-        <item x="109"/>
-        <item x="497"/>
-        <item x="512"/>
-        <item x="518"/>
-        <item x="182"/>
-        <item x="378"/>
-        <item x="371"/>
-        <item x="24"/>
-        <item x="330"/>
-        <item x="459"/>
-        <item x="47"/>
-        <item x="273"/>
-        <item x="204"/>
-        <item x="139"/>
-        <item x="485"/>
-        <item x="365"/>
-        <item x="265"/>
-        <item x="13"/>
-        <item x="286"/>
-        <item x="113"/>
-        <item x="31"/>
-        <item x="62"/>
-        <item x="320"/>
-        <item x="270"/>
-        <item x="87"/>
-        <item x="38"/>
-        <item x="86"/>
-        <item x="259"/>
-        <item x="242"/>
-        <item x="510"/>
-        <item x="338"/>
-        <item x="147"/>
-        <item x="300"/>
-        <item x="524"/>
-        <item x="201"/>
-        <item x="332"/>
-        <item x="73"/>
-        <item x="128"/>
-        <item x="15"/>
-        <item x="250"/>
-        <item x="351"/>
-        <item x="104"/>
-        <item x="169"/>
-        <item x="221"/>
-        <item x="435"/>
-        <item x="505"/>
-        <item x="117"/>
-        <item x="96"/>
-        <item x="77"/>
-        <item x="291"/>
-        <item x="243"/>
-        <item x="255"/>
-        <item x="387"/>
-        <item x="452"/>
-        <item x="347"/>
-        <item x="400"/>
-        <item x="228"/>
-        <item x="500"/>
-        <item x="468"/>
-        <item x="316"/>
-        <item x="282"/>
-        <item x="508"/>
-        <item x="11"/>
-        <item x="493"/>
-        <item x="196"/>
-        <item x="187"/>
-        <item x="55"/>
-        <item x="34"/>
-        <item x="212"/>
-        <item x="20"/>
-        <item x="457"/>
-        <item x="3"/>
-        <item x="301"/>
-        <item x="234"/>
-        <item x="322"/>
-        <item x="195"/>
-        <item x="376"/>
-        <item x="45"/>
-        <item x="413"/>
-        <item x="288"/>
-        <item x="389"/>
-        <item x="105"/>
-        <item x="278"/>
-        <item x="382"/>
-        <item x="372"/>
-        <item x="210"/>
-        <item x="153"/>
-        <item x="276"/>
-        <item x="126"/>
-        <item x="61"/>
-        <item x="95"/>
-        <item x="90"/>
-        <item x="494"/>
-        <item x="309"/>
-        <item x="317"/>
-        <item x="138"/>
-        <item x="50"/>
-        <item x="274"/>
-        <item x="63"/>
-        <item x="464"/>
-        <item x="82"/>
-        <item x="133"/>
-        <item x="159"/>
-        <item x="520"/>
-        <item x="140"/>
-        <item x="523"/>
-        <item x="467"/>
-        <item x="299"/>
-        <item x="120"/>
-        <item x="481"/>
-        <item x="349"/>
-        <item x="455"/>
-        <item x="74"/>
-        <item x="186"/>
-        <item x="454"/>
-        <item x="406"/>
-        <item x="54"/>
-        <item x="94"/>
-        <item x="230"/>
-        <item x="227"/>
-        <item x="76"/>
-        <item x="137"/>
-        <item x="26"/>
-        <item x="355"/>
-        <item x="461"/>
-        <item x="418"/>
-        <item x="257"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="447"/>
-        <item x="511"/>
-        <item x="448"/>
-        <item x="420"/>
-        <item x="293"/>
-        <item x="185"/>
-        <item x="130"/>
-        <item x="263"/>
-        <item x="297"/>
-        <item x="396"/>
-        <item x="289"/>
-        <item x="203"/>
-        <item x="80"/>
-        <item x="156"/>
-        <item x="199"/>
-        <item x="327"/>
-        <item x="373"/>
-        <item x="264"/>
-        <item x="246"/>
-        <item x="251"/>
-        <item x="296"/>
-        <item x="125"/>
-        <item x="528"/>
-        <item x="294"/>
-        <item x="390"/>
-        <item x="134"/>
-        <item x="222"/>
-        <item x="37"/>
-        <item x="1"/>
-        <item x="9"/>
-        <item x="519"/>
-        <item x="473"/>
-        <item x="151"/>
-        <item x="108"/>
-        <item x="318"/>
-        <item x="517"/>
-        <item x="529"/>
-        <item x="85"/>
-        <item x="335"/>
-        <item x="463"/>
-        <item x="238"/>
-        <item x="509"/>
-        <item x="97"/>
-        <item x="476"/>
-        <item x="202"/>
-        <item x="409"/>
-        <item x="475"/>
-        <item x="356"/>
-        <item x="240"/>
-        <item x="391"/>
-        <item x="2"/>
-        <item x="474"/>
-        <item x="129"/>
-        <item x="83"/>
-        <item x="380"/>
-        <item x="249"/>
-        <item x="176"/>
-        <item x="306"/>
-        <item x="398"/>
-        <item x="155"/>
-        <item x="402"/>
-        <item x="205"/>
-        <item x="165"/>
-        <item x="115"/>
-        <item x="329"/>
-        <item x="428"/>
-        <item x="65"/>
-        <item x="179"/>
-        <item x="359"/>
-        <item x="51"/>
-        <item x="408"/>
-        <item x="360"/>
-        <item x="244"/>
-        <item x="295"/>
-        <item x="277"/>
-        <item x="241"/>
-        <item x="124"/>
-        <item x="324"/>
-        <item x="33"/>
-        <item x="465"/>
-        <item x="392"/>
-        <item x="377"/>
-        <item x="444"/>
-        <item x="456"/>
-        <item x="352"/>
-        <item x="337"/>
-        <item x="183"/>
-        <item x="348"/>
-        <item x="235"/>
-        <item x="132"/>
-        <item x="411"/>
-        <item x="218"/>
-        <item x="434"/>
-        <item x="458"/>
-        <item x="495"/>
-        <item x="49"/>
-        <item x="122"/>
-        <item x="68"/>
-        <item x="198"/>
-        <item x="366"/>
-        <item x="231"/>
-        <item x="462"/>
-        <item x="535"/>
-        <item x="502"/>
-        <item x="307"/>
-        <item x="258"/>
-        <item x="247"/>
-        <item x="146"/>
-        <item x="272"/>
-        <item x="526"/>
-        <item x="121"/>
-        <item x="357"/>
-        <item x="531"/>
-        <item x="111"/>
-        <item x="100"/>
-        <item x="18"/>
-        <item x="271"/>
-        <item x="480"/>
-        <item x="70"/>
-        <item x="379"/>
-        <item x="346"/>
-        <item x="469"/>
-        <item x="233"/>
-        <item x="439"/>
-        <item x="292"/>
-        <item x="192"/>
-        <item x="268"/>
-        <item x="503"/>
-        <item x="403"/>
-        <item x="381"/>
-        <item x="333"/>
-        <item x="150"/>
-        <item x="245"/>
-        <item x="440"/>
-        <item x="175"/>
-        <item x="432"/>
-        <item x="303"/>
-        <item x="197"/>
-        <item x="431"/>
-        <item x="163"/>
-        <item x="422"/>
-        <item x="102"/>
-        <item x="8"/>
-        <item x="220"/>
-        <item x="383"/>
-        <item x="341"/>
-        <item x="302"/>
-        <item x="224"/>
-        <item x="254"/>
-        <item x="445"/>
-        <item x="533"/>
-        <item x="148"/>
-        <item x="433"/>
-        <item x="170"/>
-        <item x="161"/>
-        <item x="211"/>
-        <item x="527"/>
-        <item x="41"/>
-        <item x="313"/>
-        <item x="362"/>
-        <item x="177"/>
-        <item x="25"/>
-        <item x="21"/>
-        <item x="17"/>
-        <item x="487"/>
-        <item x="344"/>
-        <item x="312"/>
-        <item x="71"/>
-        <item x="12"/>
-        <item x="442"/>
-        <item x="394"/>
-        <item x="226"/>
-        <item x="471"/>
-        <item x="143"/>
-        <item x="29"/>
-        <item x="43"/>
-        <item x="144"/>
-        <item x="112"/>
-        <item x="16"/>
-        <item x="236"/>
-        <item x="252"/>
-        <item x="162"/>
-        <item x="453"/>
-        <item x="419"/>
-        <item x="118"/>
-        <item x="506"/>
-        <item x="484"/>
-        <item x="486"/>
-        <item x="478"/>
-        <item x="174"/>
-        <item x="67"/>
-        <item x="410"/>
-        <item x="449"/>
-        <item x="142"/>
-        <item x="269"/>
-        <item x="267"/>
-        <item x="450"/>
-        <item x="425"/>
-        <item x="207"/>
-        <item x="534"/>
-        <item x="110"/>
-        <item x="180"/>
-        <item x="417"/>
-        <item x="101"/>
-        <item x="298"/>
-        <item x="114"/>
-        <item x="441"/>
-        <item x="477"/>
-        <item x="499"/>
-        <item x="167"/>
-        <item x="10"/>
-        <item x="405"/>
-        <item x="281"/>
-        <item x="331"/>
-        <item x="490"/>
-        <item x="427"/>
-        <item x="501"/>
-        <item x="340"/>
-        <item x="446"/>
-        <item x="285"/>
-        <item x="208"/>
-        <item x="214"/>
-        <item x="451"/>
-        <item x="280"/>
-        <item x="472"/>
-        <item x="525"/>
-        <item x="507"/>
-        <item x="66"/>
-        <item x="521"/>
-        <item x="60"/>
-        <item x="5"/>
-        <item x="239"/>
-        <item x="116"/>
-        <item x="266"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="17">
-        <item x="7"/>
-        <item x="11"/>
-        <item x="10"/>
-        <item x="12"/>
-        <item x="15"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="14"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="13">
-        <item x="11"/>
-        <item x="5"/>
-        <item x="3"/>
-        <item x="10"/>
-        <item x="6"/>
-        <item x="1"/>
-        <item x="8"/>
-        <item x="7"/>
-        <item x="9"/>
-        <item x="0"/>
-        <item x="2"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="4" showAll="0">
-      <items count="331">
-        <item x="264"/>
-        <item x="31"/>
-        <item x="192"/>
-        <item x="280"/>
-        <item x="131"/>
-        <item x="91"/>
-        <item x="184"/>
-        <item x="19"/>
-        <item x="203"/>
-        <item x="289"/>
-        <item x="199"/>
-        <item x="166"/>
-        <item x="265"/>
-        <item x="95"/>
-        <item x="70"/>
-        <item x="266"/>
-        <item x="172"/>
-        <item x="40"/>
-        <item x="18"/>
-        <item x="57"/>
-        <item x="159"/>
-        <item x="251"/>
-        <item x="55"/>
-        <item x="119"/>
-        <item x="193"/>
-        <item x="82"/>
-        <item x="133"/>
-        <item x="155"/>
-        <item x="128"/>
-        <item x="107"/>
-        <item x="294"/>
-        <item x="205"/>
-        <item x="129"/>
-        <item x="51"/>
-        <item x="115"/>
-        <item x="94"/>
-        <item x="104"/>
-        <item x="67"/>
-        <item x="271"/>
-        <item x="6"/>
-        <item x="202"/>
-        <item x="34"/>
-        <item x="149"/>
-        <item x="44"/>
-        <item x="135"/>
-        <item x="153"/>
-        <item x="183"/>
-        <item x="14"/>
-        <item x="71"/>
-        <item x="144"/>
-        <item x="32"/>
-        <item x="260"/>
-        <item x="298"/>
-        <item x="238"/>
-        <item x="33"/>
-        <item x="142"/>
-        <item x="219"/>
-        <item x="243"/>
-        <item x="77"/>
-        <item x="296"/>
-        <item x="151"/>
-        <item x="256"/>
-        <item x="209"/>
-        <item x="242"/>
-        <item x="187"/>
-        <item x="117"/>
-        <item x="249"/>
-        <item x="164"/>
-        <item x="175"/>
-        <item x="27"/>
-        <item x="68"/>
-        <item x="61"/>
-        <item x="41"/>
-        <item x="140"/>
-        <item x="21"/>
-        <item x="120"/>
-        <item x="165"/>
-        <item x="146"/>
-        <item x="278"/>
-        <item x="308"/>
-        <item x="97"/>
-        <item x="4"/>
-        <item x="241"/>
-        <item x="309"/>
-        <item x="111"/>
-        <item x="99"/>
-        <item x="114"/>
-        <item x="37"/>
-        <item x="329"/>
-        <item x="319"/>
-        <item x="110"/>
-        <item x="83"/>
-        <item x="254"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="324"/>
-        <item x="143"/>
-        <item x="288"/>
-        <item x="220"/>
-        <item x="88"/>
-        <item x="148"/>
-        <item x="274"/>
-        <item x="103"/>
-        <item x="124"/>
-        <item x="39"/>
-        <item x="214"/>
-        <item x="277"/>
-        <item x="5"/>
-        <item x="305"/>
-        <item x="318"/>
-        <item x="72"/>
-        <item x="287"/>
-        <item x="116"/>
-        <item x="112"/>
-        <item x="236"/>
-        <item x="321"/>
-        <item x="237"/>
-        <item x="178"/>
-        <item x="162"/>
-        <item x="36"/>
-        <item x="89"/>
-        <item x="224"/>
-        <item x="198"/>
-        <item x="284"/>
-        <item x="190"/>
-        <item x="62"/>
-        <item x="169"/>
-        <item x="204"/>
-        <item x="98"/>
-        <item x="22"/>
-        <item x="253"/>
-        <item x="50"/>
-        <item x="170"/>
-        <item x="156"/>
-        <item x="317"/>
-        <item x="15"/>
-        <item x="81"/>
-        <item x="85"/>
-        <item x="157"/>
-        <item x="59"/>
-        <item x="66"/>
-        <item x="234"/>
-        <item x="245"/>
-        <item x="141"/>
-        <item x="229"/>
-        <item x="54"/>
-        <item x="263"/>
-        <item x="125"/>
-        <item x="315"/>
-        <item x="3"/>
-        <item x="160"/>
-        <item x="240"/>
-        <item x="200"/>
-        <item x="171"/>
-        <item x="13"/>
-        <item x="176"/>
-        <item x="230"/>
-        <item x="106"/>
-        <item x="20"/>
-        <item x="75"/>
-        <item x="16"/>
-        <item x="228"/>
-        <item x="53"/>
-        <item x="215"/>
-        <item x="258"/>
-        <item x="320"/>
-        <item x="268"/>
-        <item x="255"/>
-        <item x="262"/>
-        <item x="206"/>
-        <item x="173"/>
-        <item x="225"/>
-        <item x="180"/>
-        <item x="325"/>
-        <item x="191"/>
-        <item x="300"/>
-        <item x="127"/>
-        <item x="207"/>
-        <item x="47"/>
-        <item x="259"/>
-        <item x="306"/>
-        <item x="292"/>
-        <item x="10"/>
-        <item x="314"/>
-        <item x="76"/>
-        <item x="322"/>
-        <item x="113"/>
-        <item x="42"/>
-        <item x="17"/>
-        <item x="186"/>
-        <item x="73"/>
-        <item x="26"/>
-        <item x="0"/>
-        <item x="293"/>
-        <item x="87"/>
-        <item x="56"/>
-        <item x="212"/>
-        <item x="312"/>
-        <item x="247"/>
-        <item x="132"/>
-        <item x="161"/>
-        <item x="101"/>
-        <item x="28"/>
-        <item x="147"/>
-        <item x="233"/>
-        <item x="210"/>
-        <item x="137"/>
-        <item x="45"/>
-        <item x="195"/>
-        <item x="181"/>
-        <item x="313"/>
-        <item x="261"/>
-        <item x="239"/>
-        <item x="307"/>
-        <item x="299"/>
-        <item x="250"/>
-        <item x="58"/>
-        <item x="235"/>
-        <item x="188"/>
-        <item x="316"/>
-        <item x="189"/>
-        <item x="23"/>
-        <item x="138"/>
-        <item x="226"/>
-        <item x="244"/>
-        <item x="213"/>
-        <item x="96"/>
-        <item x="38"/>
-        <item x="168"/>
-        <item x="86"/>
-        <item x="167"/>
-        <item x="48"/>
-        <item x="273"/>
-        <item x="11"/>
-        <item x="201"/>
-        <item x="78"/>
-        <item x="276"/>
-        <item x="63"/>
-        <item x="100"/>
-        <item x="60"/>
-        <item x="49"/>
-        <item x="327"/>
-        <item x="182"/>
-        <item x="69"/>
-        <item x="64"/>
-        <item x="248"/>
-        <item x="270"/>
-        <item x="102"/>
-        <item x="24"/>
-        <item x="8"/>
-        <item x="139"/>
-        <item x="279"/>
-        <item x="12"/>
-        <item x="328"/>
-        <item x="179"/>
-        <item x="295"/>
-        <item x="158"/>
-        <item x="109"/>
-        <item x="275"/>
-        <item x="123"/>
-        <item x="282"/>
-        <item x="25"/>
-        <item x="145"/>
-        <item x="194"/>
-        <item x="218"/>
-        <item x="46"/>
-        <item x="303"/>
-        <item x="154"/>
-        <item x="35"/>
-        <item x="208"/>
-        <item x="122"/>
-        <item x="105"/>
-        <item x="126"/>
-        <item x="80"/>
-        <item x="108"/>
-        <item x="231"/>
-        <item x="281"/>
-        <item x="272"/>
-        <item x="150"/>
-        <item x="7"/>
-        <item x="304"/>
-        <item x="177"/>
-        <item x="163"/>
-        <item x="257"/>
-        <item x="65"/>
-        <item x="121"/>
-        <item x="79"/>
-        <item x="227"/>
-        <item x="134"/>
-        <item x="283"/>
-        <item x="232"/>
-        <item x="90"/>
-        <item x="152"/>
-        <item x="301"/>
-        <item x="311"/>
-        <item x="130"/>
-        <item x="197"/>
-        <item x="267"/>
-        <item x="30"/>
-        <item x="217"/>
-        <item x="297"/>
-        <item x="302"/>
-        <item x="84"/>
-        <item x="216"/>
-        <item x="74"/>
-        <item x="1"/>
-        <item x="222"/>
-        <item x="196"/>
-        <item x="118"/>
-        <item x="136"/>
-        <item x="221"/>
-        <item x="252"/>
-        <item x="52"/>
-        <item x="211"/>
-        <item x="290"/>
-        <item x="223"/>
-        <item x="174"/>
-        <item x="291"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="185"/>
-        <item x="310"/>
-        <item x="269"/>
-        <item x="323"/>
-        <item x="286"/>
-        <item x="246"/>
-        <item x="43"/>
-        <item x="326"/>
-        <item x="285"/>
-        <item x="29"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="4" showAll="0"/>
-    <pivotField dataField="1" numFmtId="4" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0" defaultSubtotal="0">
-      <items count="14">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0" defaultSubtotal="0"/>
-    <pivotField showAll="0" defaultSubtotal="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Profit" fld="12" baseField="0" baseItem="0" numFmtId="4"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="7" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Sales" xr10:uid="{1221E4DF-EE34-4853-99D2-909E42BA9762}" sourceName="Sales">
   <pivotTables>
@@ -94883,28 +95647,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="14" t="s">
         <v>1411</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="E1" s="20" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="E1" s="15" t="s">
         <v>1420</v>
       </c>
-      <c r="F1" s="21"/>
-      <c r="H1" s="9" t="s">
+      <c r="F1" s="16"/>
+      <c r="H1" s="14" t="s">
         <v>1412</v>
       </c>
-      <c r="I1" s="10"/>
-      <c r="K1" s="11" t="s">
+      <c r="I1" s="17"/>
+      <c r="K1" s="18" t="s">
         <v>1413</v>
       </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="10"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -94942,7 +95706,7 @@
       <c r="B4" s="2">
         <v>2457672.5</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4">
         <v>80</v>
       </c>
       <c r="E4" s="4" t="s">
@@ -94986,7 +95750,7 @@
       <c r="B5" s="2">
         <v>2053990</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5">
         <v>69</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -95004,22 +95768,22 @@
       <c r="K5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="16">
+      <c r="L5">
         <v>25</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5">
         <v>68</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5">
         <v>28</v>
       </c>
-      <c r="O5" s="16">
+      <c r="O5">
         <v>38</v>
       </c>
-      <c r="P5" s="16">
+      <c r="P5">
         <v>49</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="Q5">
         <v>208</v>
       </c>
     </row>
@@ -95030,7 +95794,7 @@
       <c r="B6" s="2">
         <v>3858527.5</v>
       </c>
-      <c r="C6" s="16">
+      <c r="C6">
         <v>93</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -95048,22 +95812,22 @@
       <c r="K6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L6" s="16">
+      <c r="L6">
         <v>30</v>
       </c>
-      <c r="M6" s="16">
+      <c r="M6">
         <v>41</v>
       </c>
-      <c r="N6" s="16">
+      <c r="N6">
         <v>44</v>
       </c>
-      <c r="O6" s="16">
+      <c r="O6">
         <v>30</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6">
         <v>28</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6">
         <v>173</v>
       </c>
     </row>
@@ -95074,7 +95838,7 @@
       <c r="B7" s="2">
         <v>3656450</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7">
         <v>96</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -95092,22 +95856,22 @@
       <c r="K7" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="16">
+      <c r="L7">
         <v>30</v>
       </c>
-      <c r="M7" s="16">
+      <c r="M7">
         <v>47</v>
       </c>
-      <c r="N7" s="16">
+      <c r="N7">
         <v>43</v>
       </c>
-      <c r="O7" s="16">
+      <c r="O7">
         <v>37</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7">
         <v>42</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7">
         <v>199</v>
       </c>
     </row>
@@ -95118,7 +95882,7 @@
       <c r="B8" s="2">
         <v>3283600</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8">
         <v>102</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -95136,22 +95900,22 @@
       <c r="K8" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="L8" s="16">
+      <c r="L8">
         <v>26</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8">
         <v>68</v>
       </c>
-      <c r="N8" s="16">
+      <c r="N8">
         <v>35</v>
       </c>
-      <c r="O8" s="16">
+      <c r="O8">
         <v>46</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8">
         <v>39</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8">
         <v>214</v>
       </c>
     </row>
@@ -95162,7 +95926,7 @@
       <c r="B9" s="2">
         <v>2302180</v>
       </c>
-      <c r="C9" s="16">
+      <c r="C9">
         <v>67</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -95180,22 +95944,22 @@
       <c r="K9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="L9" s="16">
+      <c r="L9">
         <v>33</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9">
         <v>54</v>
       </c>
-      <c r="N9" s="16">
+      <c r="N9">
         <v>32</v>
       </c>
-      <c r="O9" s="16">
+      <c r="O9">
         <v>38</v>
       </c>
-      <c r="P9" s="16">
+      <c r="P9">
         <v>49</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9">
         <v>206</v>
       </c>
     </row>
@@ -95206,7 +95970,7 @@
       <c r="B10" s="2">
         <v>2418467.5</v>
       </c>
-      <c r="C10" s="16">
+      <c r="C10">
         <v>89</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -95224,22 +95988,22 @@
       <c r="K10" s="4" t="s">
         <v>1394</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10">
         <v>144</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10">
         <v>278</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10">
         <v>182</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10">
         <v>189</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10">
         <v>207</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10">
         <v>1000</v>
       </c>
     </row>
@@ -95250,7 +96014,7 @@
       <c r="B11" s="2">
         <v>3946550</v>
       </c>
-      <c r="C11" s="16">
+      <c r="C11">
         <v>87</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -95273,7 +96037,7 @@
       <c r="B12" s="2">
         <v>3116112.5</v>
       </c>
-      <c r="C12" s="16">
+      <c r="C12">
         <v>86</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -95296,7 +96060,7 @@
       <c r="B13" s="2">
         <v>2887077.5</v>
       </c>
-      <c r="C13" s="16">
+      <c r="C13">
         <v>82</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -95319,7 +96083,7 @@
       <c r="B14" s="2">
         <v>2722897.5</v>
       </c>
-      <c r="C14" s="16">
+      <c r="C14">
         <v>72</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -95342,7 +96106,7 @@
       <c r="B15" s="2">
         <v>2972965</v>
       </c>
-      <c r="C15" s="16">
+      <c r="C15">
         <v>77</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -95365,7 +96129,7 @@
       <c r="B16" s="2">
         <v>35676490</v>
       </c>
-      <c r="C16" s="16">
+      <c r="C16">
         <v>1000</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -95376,10 +96140,10 @@
       </c>
     </row>
     <row r="18" spans="2:3" ht="21" x14ac:dyDescent="0.4">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="19" t="s">
         <v>1414</v>
       </c>
-      <c r="C18" s="11"/>
+      <c r="C18" s="18"/>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B20" s="3" t="s">
@@ -95455,17 +96219,17 @@
   <sheetData>
     <row r="1" spans="1:22" ht="19.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7"/>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
       <c r="O1" s="7"/>
@@ -95537,7 +96301,7 @@
       <c r="I4" s="5"/>
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
-      <c r="L4" s="13"/>
+      <c r="L4" s="8"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
@@ -95560,8 +96324,8 @@
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -95584,22 +96348,22 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
-      <c r="K6" s="15" t="s">
+      <c r="K6" s="10" t="s">
         <v>1416</v>
       </c>
       <c r="L6" s="5"/>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="10" t="s">
         <v>1417</v>
       </c>
       <c r="N6" s="5"/>
-      <c r="O6" s="15" t="s">
+      <c r="O6" s="10" t="s">
         <v>1418</v>
       </c>
       <c r="P6" s="5"/>
-      <c r="Q6" s="15" t="s">
+      <c r="Q6" s="10" t="s">
         <v>1419</v>
       </c>
-      <c r="R6" s="14"/>
+      <c r="R6" s="9"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
       <c r="U6" s="5"/>
@@ -95616,22 +96380,22 @@
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
-      <c r="K7" s="17">
+      <c r="K7" s="11">
         <f>SUM('Retail Sales Data'!J:J)</f>
         <v>35676490</v>
       </c>
       <c r="L7" s="5"/>
-      <c r="M7" s="18">
+      <c r="M7" s="12">
         <f>SUM('Retail Sales Data'!M:M)</f>
         <v>6275825.6199999992</v>
       </c>
       <c r="N7" s="5"/>
-      <c r="O7" s="19">
+      <c r="O7" s="10">
         <f>COUNTA('Retail Sales Data'!A:A)</f>
         <v>1001</v>
       </c>
       <c r="P7" s="5"/>
-      <c r="Q7" s="19">
+      <c r="Q7" s="10">
         <f>SUM('Retail Sales Data'!K:K)</f>
         <v>3491</v>
       </c>
